--- a/data/research/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -758,8 +758,110 @@
       <c r="AI2" s="2" t="inlineStr"/>
       <c r="AJ2" s="2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>f5da3ee6534e40b5</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>dd15133f8ac3980e0e8f9507ceb080d57ad35a633e2d504e0df7fc9cdc098a3f</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>0.687866</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>0.12839463436123344</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:20.152893Z</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ2"/>
+  <autoFilter ref="A1:AJ3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -860,8 +860,212 @@
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>7f1dace6577c49d6</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28ac6bf9357568fc0f221f5991e8dfb85aef9e50cc37b94a93280592039ef596</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0.687866</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>0.12839463436123344</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:40.200411Z</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>640321a3ee764d40</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3b481b72458f95998f81ca892704b4ac7dca0dff8b1583067f4c8fae4d84ff0d</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0.687866</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0.12839463436123344</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:39.258654Z</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ3"/>
+  <autoFilter ref="A1:AJ5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1064,8 +1064,110 @@
       <c r="AI5" s="2" t="inlineStr"/>
       <c r="AJ5" s="2" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ac8c9b72b5da46fd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>bcd7d4bdd1e2218dd22c32e053e9e1e56eeed1afdf8b775edd90e5369a90ae7e</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0.687866</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0.12839463436123344</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:46.828865Z</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ5"/>
+  <autoFilter ref="A1:AJ6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AJ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1166,8 +1166,110 @@
       <c r="AI6" s="2" t="inlineStr"/>
       <c r="AJ6" s="2" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>88a54cf4e97540e8</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8e17bc625b6f663721d0cd0b27f30cf8017a2cbaa61c81881824fbb2600f16d7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0.687866</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>0.12839463436123344</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:09:15.062801Z</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ6"/>
+  <autoFilter ref="A1:AJ7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ7"/>
+  <dimension ref="A1:AJ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1268,8 +1268,110 @@
       <c r="AI7" s="2" t="inlineStr"/>
       <c r="AJ7" s="2" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>8e4da1d39903423d</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>cb2508545871cd245c79cd37a7ddf28f5f869bf875eba85e1d6069b628af9a62</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0.687866</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0.12839463436123344</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:03.516712Z</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ7"/>
+  <autoFilter ref="A1:AJ8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ8"/>
+  <dimension ref="A1:AJ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1370,8 +1370,4800 @@
       <c r="AI8" s="2" t="inlineStr"/>
       <c r="AJ8" s="2" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>1175df5ac4a24f7e</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9c5f1e0498568c8c9d9ce690d9b28bbb93b8c82b61f0585c72a5fa45be3b22f5</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0.687866</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0.12839463436123344</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:55:15.811302Z</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>937c22f799134c43</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>c5e574fce81b754746d25bd1be4a70938cce553267554fb8aa28996355ec028c</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0.688438</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0.12896663436123346</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:32:07.176804Z</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>946d34c99db5494a</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3aec5c18e4baa0f9a1c7ddffe59287913cd115137d2a3b4af2f4e69f0595f97f</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.688438</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>0.10860606722689081</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:17:10.490431Z</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>c0efb8476b5e4c0c</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3aec5c18e4baa0f9a1c7ddffe59287913cd115137d2a3b4af2f4e69f0595f97f</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>70303</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.622594</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.20242593277310922</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:17:11.536317Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>54237935f8cf47aa</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3aec5c18e4baa0f9a1c7ddffe59287913cd115137d2a3b4af2f4e69f0595f97f</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>70046</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.838894</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0.15838281789137387</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:17:12.000249Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ad6c249080bb49d5</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3aec5c18e4baa0f9a1c7ddffe59287913cd115137d2a3b4af2f4e69f0595f97f</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.558196</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>-0.04180400000000006</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:17:12.498644Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>0168ee32155241b8</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3aec5c18e4baa0f9a1c7ddffe59287913cd115137d2a3b4af2f4e69f0595f97f</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0.570811</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0.04029456807511733</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:17:13.488700Z</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>13cf6b101cd24a76</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3aec5c18e4baa0f9a1c7ddffe59287913cd115137d2a3b4af2f4e69f0595f97f</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>70306</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0.572663</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>-0.10784818210862612</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:17:13.972415Z</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>0140478aad8c4bcb</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6d4544b49d1d638f1deb4234c0e0c01fa8fbae11f01c2a2fc60b31712569fb95</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0.688438</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>0.079063</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:47:24.674109Z</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>0f8bd3e538dc4373</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6d4544b49d1d638f1deb4234c0e0c01fa8fbae11f01c2a2fc60b31712569fb95</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>70303</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0.622594</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>0.23196899999999998</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:47:25.733915Z</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>130ca8ffb1244d0e</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6d4544b49d1d638f1deb4234c0e0c01fa8fbae11f01c2a2fc60b31712569fb95</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0.558196</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>-0.051178999999999975</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:47:26.845751Z</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>1422789bd4f04502</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6d4544b49d1d638f1deb4234c0e0c01fa8fbae11f01c2a2fc60b31712569fb95</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0.78276</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>0.08306030030030032</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:47:27.432081Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>bf06070b56d644c2</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>6d4544b49d1d638f1deb4234c0e0c01fa8fbae11f01c2a2fc60b31712569fb95</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0.570811</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>0.02126145045045047</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:47:27.967852Z</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>8b64280d2c93480a</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0.688438</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0.058808370370370455</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:20:21.088131Z</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>0.630000</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0.000370</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>1.1765</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:06:42.874068Z</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>543ee3a29e64458c</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>70303</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0.622594</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0.23196899999999998</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:20:22.245034Z</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>142736edd53f47ca</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0.558196</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>-0.07143362962962951</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:20:23.543914Z</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>4885fb6097cd4019</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0.78276</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.08306030030030032</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:20:24.118010Z</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>f5e43b2c385f4fa4</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0.570811</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>0.031640493087557564</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:20:24.656879Z</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>07efa7e5a36a4a86</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>533fea08f6899886856a22c8b82fe2bc1d4c49576971024283434d4b7315bbc9</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>70303</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0.622594</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>0.23196899999999998</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:32:30.412423Z</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>0.390000</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>-0.000625</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>-1.5000</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:55:54.403218Z</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>c6e2d94a10034fe3</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>533fea08f6899886856a22c8b82fe2bc1d4c49576971024283434d4b7315bbc9</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0.558196</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>-0.07143362962962951</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:32:31.491970Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>d6db443346f44e7e</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>533fea08f6899886856a22c8b82fe2bc1d4c49576971024283434d4b7315bbc9</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0.78276</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>0.08306030030030032</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:32:32.038017Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>1c96fe98a95146cf</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>533fea08f6899886856a22c8b82fe2bc1d4c49576971024283434d4b7315bbc9</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0.570811</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0.031640493087557564</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:32:32.495232Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>d61ac3966e604b3f</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>df737ccc747168411051ce1a17c4ba0d065ba4d5b92bad2d63306ee6a3d852ad</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0.558196</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>-0.03196793442622947</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:15:50.661222Z</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>31392df741614485</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>df737ccc747168411051ce1a17c4ba0d065ba4d5b92bad2d63306ee6a3d852ad</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0.78276</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>0.08306030030030032</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:15:51.151586Z</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr"/>
+      <c r="AI32" s="2" t="inlineStr"/>
+      <c r="AJ32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>1acbfa9c8bf947db</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>df737ccc747168411051ce1a17c4ba0d065ba4d5b92bad2d63306ee6a3d852ad</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0.570811</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>0.04029456807511733</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:15:51.693288Z</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr"/>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>1e66fa2e4c2d468f</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>7622acb01e75f8c072abce75d7db6c9e6cede883a38c71cb50ddb09cb5b70653</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>0.558196</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>-0.03196793442622947</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:14.997846Z</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr"/>
+      <c r="AH34" s="2" t="inlineStr"/>
+      <c r="AI34" s="2" t="inlineStr"/>
+      <c r="AJ34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>b246b001d21a4d27</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>7622acb01e75f8c072abce75d7db6c9e6cede883a38c71cb50ddb09cb5b70653</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>0.78276</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0.08306030030030032</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:15.479941Z</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr"/>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr"/>
+      <c r="AI35" s="2" t="inlineStr"/>
+      <c r="AJ35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>94e35d7497c6454c</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>7622acb01e75f8c072abce75d7db6c9e6cede883a38c71cb50ddb09cb5b70653</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0.570811</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>0.04029456807511733</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:16.010693Z</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="2" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr"/>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2063078301144b73</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>528639205c5899c0cdf1bae7bf1adfb5d019bc11e79b9bc778f8eb3bb742ae6e</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>0.557781</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>-0.032382934426229526</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:42.011106Z</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>0.590000</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>-0.000164</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0.6944</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:52:24.921040Z</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
+      <c r="AJ37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>8ed27445e4314caa</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>528639205c5899c0cdf1bae7bf1adfb5d019bc11e79b9bc778f8eb3bb742ae6e</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>0.75532</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>0.055620300300300296</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:42.630829Z</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>c0e036cb4a6144ae</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>528639205c5899c0cdf1bae7bf1adfb5d019bc11e79b9bc778f8eb3bb742ae6e</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>0.571416</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>0.04089956807511741</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:43.200159Z</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>b89362327e7e4a1a</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>0.75532</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0.055620300300300296</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:33.121525Z</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>0.700000</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>0.000300</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>-2.0000</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:55:33.181594Z</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>1390b2b1384e49e1</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>0.571416</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0.04089956807511741</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:33.684542Z</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>0.530000</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>-0.000516</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>-1.2500</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:52:00.689578Z</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AI41" s="2" t="inlineStr"/>
+      <c r="AJ41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ec9fd1dc55e34abb</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>7ace8d7f4fbdc070e08f34cd2d87e611d8a11ea9c84bc16f6b2fe3e657ef1885</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>70684</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>0.701456</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0.06116823021582729</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:56:17.211441Z</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr"/>
+      <c r="AI42" s="2" t="inlineStr"/>
+      <c r="AJ42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>0b7491c30c164b9a</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>e6397d2918a4f8d2740c3e391db4fc80f2b0d7dd878a55ec7bddc08c3c8f6d3a</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>70684</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0.701456</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0.08168413688212928</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:30:56.031962Z</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr"/>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
+      <c r="AJ43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>538df7a378ec4180</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>953254c9a540a32068da1d4c7a137a83eba7ac85928e5d1f97d86fe5722f659e</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>70684</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0.701456</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>0.08168413688212928</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:51:11.898057Z</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr"/>
+      <c r="AI44" s="2" t="inlineStr"/>
+      <c r="AJ44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>04bcb919abcf42c3</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>1d5767148be99bbdefb05ee62b311a488896c7db143acb8c72817e0684151342</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>70684</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>0.701456</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>0.08168413688212928</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:08:42.352133Z</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr"/>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>6d8101a7bafe4ccc</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>6ebc3dc87966ac0e4ece82f0be01d591436ac7878b0a7963581ff09841f3512b</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>70891</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>0.720237</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>0.050270003300330046</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:54:45.400838Z</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr"/>
+      <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="2" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr"/>
+      <c r="AI46" s="2" t="inlineStr"/>
+      <c r="AJ46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>dd3d77be76414c1e</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>6ebc3dc87966ac0e4ece82f0be01d591436ac7878b0a7963581ff09841f3512b</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>70684</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>0.701927</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0.11176306557377047</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:54:45.902441Z</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr"/>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AI47" s="2" t="inlineStr"/>
+      <c r="AJ47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>4fee25312eb242c6</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>a27f6de2541f20b99eb176b999d4f6f123e8edc49671c0497c4d08e67a0aa19f</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>70891</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>0.720685</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0.040173817891373864</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:57:48.356454Z</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr"/>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr"/>
+      <c r="AI48" s="2" t="inlineStr"/>
+      <c r="AJ48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>be669549a2d04c7a</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>a27f6de2541f20b99eb176b999d4f6f123e8edc49671c0497c4d08e67a0aa19f</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>70684</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>0.701803</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0.09242799999999995</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:57:48.837336Z</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AI49" s="2" t="inlineStr"/>
+      <c r="AJ49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>de8200c3de4145a2</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>70891</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>0.720685</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>0.020985300300300325</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:39.542403Z</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="2" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr"/>
+      <c r="AI50" s="2" t="inlineStr"/>
+      <c r="AJ50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>fe546a675f8d4f95</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>70684</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>0.701803</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>0.09242799999999995</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:40.034960Z</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr"/>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AI51" s="2" t="inlineStr"/>
+      <c r="AJ51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>5854cc82e82146f4</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>71393</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>0.535922</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>-0.13404499669966996</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:40.568093Z</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr"/>
+      <c r="AE52" s="2" t="inlineStr"/>
+      <c r="AF52" s="2" t="inlineStr"/>
+      <c r="AG52" s="2" t="inlineStr"/>
+      <c r="AH52" s="2" t="inlineStr"/>
+      <c r="AI52" s="2" t="inlineStr"/>
+      <c r="AJ52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>6fd00c7e4f0649a6</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>71323</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>0.63019</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>0.050358067226890846</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.112906Z</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr"/>
+      <c r="AE53" s="2" t="inlineStr"/>
+      <c r="AF53" s="2" t="inlineStr"/>
+      <c r="AG53" s="2" t="inlineStr"/>
+      <c r="AH53" s="2" t="inlineStr"/>
+      <c r="AI53" s="2" t="inlineStr"/>
+      <c r="AJ53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>f754ffd357b74391</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>71394</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>0.599177</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>-0.05117265034965035</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.677954Z</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr"/>
+      <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AG54" s="2" t="inlineStr"/>
+      <c r="AH54" s="2" t="inlineStr"/>
+      <c r="AI54" s="2" t="inlineStr"/>
+      <c r="AJ54" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ8"/>
+  <autoFilter ref="A1:AJ54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ54"/>
+  <dimension ref="A1:AJ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6162,8 +6162,824 @@
       <c r="AI54" s="2" t="inlineStr"/>
       <c r="AJ54" s="2" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>3fd5550e759d4cd5</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>e92cb80e37989eb339f82c2ea4e6ba64db30a7a6a86ac411b645de94d07c6235</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>70684</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>0.701803</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>0.09242799999999995</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:18.767211Z</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr"/>
+      <c r="AE55" s="2" t="inlineStr"/>
+      <c r="AF55" s="2" t="inlineStr"/>
+      <c r="AG55" s="2" t="inlineStr"/>
+      <c r="AH55" s="2" t="inlineStr"/>
+      <c r="AI55" s="2" t="inlineStr"/>
+      <c r="AJ55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>7a8d9f015a44430d</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>e92cb80e37989eb339f82c2ea4e6ba64db30a7a6a86ac411b645de94d07c6235</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>71393</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>0.535922</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>-0.13404499669966996</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:19.583223Z</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr"/>
+      <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr"/>
+      <c r="AG56" s="2" t="inlineStr"/>
+      <c r="AH56" s="2" t="inlineStr"/>
+      <c r="AI56" s="2" t="inlineStr"/>
+      <c r="AJ56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>b582049e70ce4cb5</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>e92cb80e37989eb339f82c2ea4e6ba64db30a7a6a86ac411b645de94d07c6235</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>71323</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>0.63019</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>0.04002606557377053</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:20.288019Z</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr"/>
+      <c r="AE57" s="2" t="inlineStr"/>
+      <c r="AF57" s="2" t="inlineStr"/>
+      <c r="AG57" s="2" t="inlineStr"/>
+      <c r="AH57" s="2" t="inlineStr"/>
+      <c r="AI57" s="2" t="inlineStr"/>
+      <c r="AJ57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>facd0ca842694261</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>e92cb80e37989eb339f82c2ea4e6ba64db30a7a6a86ac411b645de94d07c6235</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>71394</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>0.599177</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>-0.05117265034965035</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:20.846474Z</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr"/>
+      <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr"/>
+      <c r="AG58" s="2" t="inlineStr"/>
+      <c r="AH58" s="2" t="inlineStr"/>
+      <c r="AI58" s="2" t="inlineStr"/>
+      <c r="AJ58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>aee8601eea0243ef</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>70684</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>0.701803</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>0.12197106722689077</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:22.344795Z</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr"/>
+      <c r="AE59" s="2" t="inlineStr"/>
+      <c r="AF59" s="2" t="inlineStr"/>
+      <c r="AG59" s="2" t="inlineStr"/>
+      <c r="AH59" s="2" t="inlineStr"/>
+      <c r="AI59" s="2" t="inlineStr"/>
+      <c r="AJ59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>5153397cb8c04734</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>71393</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>0.535922</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>-0.13404499669966996</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:22.969840Z</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr"/>
+      <c r="W60" s="2" t="inlineStr"/>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr"/>
+      <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AF60" s="2" t="inlineStr"/>
+      <c r="AG60" s="2" t="inlineStr"/>
+      <c r="AH60" s="2" t="inlineStr"/>
+      <c r="AI60" s="2" t="inlineStr"/>
+      <c r="AJ60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>d7f6fedeb47843ac</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>71323</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>0.63019</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>0.03018999999999994</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:23.442743Z</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr"/>
+      <c r="W61" s="2" t="inlineStr"/>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr"/>
+      <c r="AE61" s="2" t="inlineStr"/>
+      <c r="AF61" s="2" t="inlineStr"/>
+      <c r="AG61" s="2" t="inlineStr"/>
+      <c r="AH61" s="2" t="inlineStr"/>
+      <c r="AI61" s="2" t="inlineStr"/>
+      <c r="AJ61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>1ce2dff6ff524ef4</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>71394</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>0.599177</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>-0.05117265034965035</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:24.176088Z</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr"/>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr"/>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr"/>
+      <c r="AE62" s="2" t="inlineStr"/>
+      <c r="AF62" s="2" t="inlineStr"/>
+      <c r="AG62" s="2" t="inlineStr"/>
+      <c r="AH62" s="2" t="inlineStr"/>
+      <c r="AI62" s="2" t="inlineStr"/>
+      <c r="AJ62" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ54"/>
+  <autoFilter ref="A1:AJ62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ62"/>
+  <dimension ref="A1:AJ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6656,14 +6656,34 @@
       <c r="W59" s="2" t="inlineStr"/>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y59" s="2" t="inlineStr"/>
-      <c r="Z59" s="2" t="inlineStr"/>
-      <c r="AA59" s="2" t="inlineStr"/>
-      <c r="AB59" s="2" t="inlineStr"/>
-      <c r="AC59" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>0.580000</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0.000168</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1.4493</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:19.412290Z</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr"/>
       <c r="AE59" s="2" t="inlineStr"/>
       <c r="AF59" s="2" t="inlineStr"/>
@@ -6978,8 +6998,416 @@
       <c r="AI62" s="2" t="inlineStr"/>
       <c r="AJ62" s="2" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>d8128aac520944ba</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>a6c9607e653da0963c1aedbfdf02df93d0e81f5e712085073f323442476b541d</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>71323</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>0.63019</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>0.03018999999999994</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:36.421980Z</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr"/>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr"/>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr"/>
+      <c r="AE63" s="2" t="inlineStr"/>
+      <c r="AF63" s="2" t="inlineStr"/>
+      <c r="AG63" s="2" t="inlineStr"/>
+      <c r="AH63" s="2" t="inlineStr"/>
+      <c r="AI63" s="2" t="inlineStr"/>
+      <c r="AJ63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>fd16dfaee41c4759</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>a6c9607e653da0963c1aedbfdf02df93d0e81f5e712085073f323442476b541d</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>71394</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>0.599177</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>-0.05117265034965035</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:37.364465Z</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr"/>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr"/>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr"/>
+      <c r="AE64" s="2" t="inlineStr"/>
+      <c r="AF64" s="2" t="inlineStr"/>
+      <c r="AG64" s="2" t="inlineStr"/>
+      <c r="AH64" s="2" t="inlineStr"/>
+      <c r="AI64" s="2" t="inlineStr"/>
+      <c r="AJ64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>c3c5f02fc1944c76</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>8bbc4026175cb2ebe4b2e6ff2fe1095eb4b27ca11c5fee754a53806b7e282494</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>71394</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>0.599247</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>-0.051102650349650336</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:05.307890Z</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr"/>
+      <c r="AE65" s="2" t="inlineStr"/>
+      <c r="AF65" s="2" t="inlineStr"/>
+      <c r="AG65" s="2" t="inlineStr"/>
+      <c r="AH65" s="2" t="inlineStr"/>
+      <c r="AI65" s="2" t="inlineStr"/>
+      <c r="AJ65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>0fc061bba2424118</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>b921081c94f350d1171b92b678f9b1518a4a8603443c3731dc34195c91e09a2e</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>71394</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>0.599247</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>-0.051102650349650336</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:39.396089Z</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr"/>
+      <c r="W66" s="2" t="inlineStr"/>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr"/>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr"/>
+      <c r="AE66" s="2" t="inlineStr"/>
+      <c r="AF66" s="2" t="inlineStr"/>
+      <c r="AG66" s="2" t="inlineStr"/>
+      <c r="AH66" s="2" t="inlineStr"/>
+      <c r="AI66" s="2" t="inlineStr"/>
+      <c r="AJ66" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ62"/>
+  <autoFilter ref="A1:AJ66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ66"/>
+  <dimension ref="A1:AJ86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7084,14 +7084,34 @@
       <c r="W63" s="2" t="inlineStr"/>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y63" s="2" t="inlineStr"/>
-      <c r="Z63" s="2" t="inlineStr"/>
-      <c r="AA63" s="2" t="inlineStr"/>
-      <c r="AB63" s="2" t="inlineStr"/>
-      <c r="AC63" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>0.600000</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>-1.5000</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:03.048413Z</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr"/>
       <c r="AE63" s="2" t="inlineStr"/>
       <c r="AF63" s="2" t="inlineStr"/>
@@ -7390,14 +7410,34 @@
       <c r="W66" s="2" t="inlineStr"/>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y66" s="2" t="inlineStr"/>
-      <c r="Z66" s="2" t="inlineStr"/>
-      <c r="AA66" s="2" t="inlineStr"/>
-      <c r="AB66" s="2" t="inlineStr"/>
-      <c r="AC66" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>0.650000</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>-0.000350</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0.6720</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:05.296931Z</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr"/>
       <c r="AE66" s="2" t="inlineStr"/>
       <c r="AF66" s="2" t="inlineStr"/>
@@ -7406,8 +7446,2048 @@
       <c r="AI66" s="2" t="inlineStr"/>
       <c r="AJ66" s="2" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>0b5cbe7fdde440c2</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>6b68153b79acdd952b41e5c80c5357e0313e265e40ddf43ba8b3ca1a2fbe99b0</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>71970</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>0.659431</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>0.0594309999999999</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:54:13.814458Z</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr"/>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr"/>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr"/>
+      <c r="AE67" s="2" t="inlineStr"/>
+      <c r="AF67" s="2" t="inlineStr"/>
+      <c r="AG67" s="2" t="inlineStr"/>
+      <c r="AH67" s="2" t="inlineStr"/>
+      <c r="AI67" s="2" t="inlineStr"/>
+      <c r="AJ67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>4c87a44812fc4066</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>f617cb6f151897e176682c67986c97485d243bc767b189c2846660a8242f113b</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>71970</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>0.659347</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>0.05934699999999993</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:08:10.102238Z</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr"/>
+      <c r="W68" s="2" t="inlineStr"/>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr"/>
+      <c r="Z68" s="2" t="inlineStr"/>
+      <c r="AA68" s="2" t="inlineStr"/>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr"/>
+      <c r="AE68" s="2" t="inlineStr"/>
+      <c r="AF68" s="2" t="inlineStr"/>
+      <c r="AG68" s="2" t="inlineStr"/>
+      <c r="AH68" s="2" t="inlineStr"/>
+      <c r="AI68" s="2" t="inlineStr"/>
+      <c r="AJ68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>c9ff0b973ede44e2</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>85060feb5c496fb103bc90e5d86a4c227292d3b19db5f0ee6530b90f27040947</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>72079</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>0.500102</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>0.059573365638766584</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:02:38.461463Z</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="2" t="inlineStr"/>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="2" t="inlineStr"/>
+      <c r="AA69" s="2" t="inlineStr"/>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr"/>
+      <c r="AE69" s="2" t="inlineStr"/>
+      <c r="AF69" s="2" t="inlineStr"/>
+      <c r="AG69" s="2" t="inlineStr"/>
+      <c r="AH69" s="2" t="inlineStr"/>
+      <c r="AI69" s="2" t="inlineStr"/>
+      <c r="AJ69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2edafe7a001a4440</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>85060feb5c496fb103bc90e5d86a4c227292d3b19db5f0ee6530b90f27040947</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>71970</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>0.659098</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>0.05909799999999987</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:02:39.372205Z</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr"/>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr"/>
+      <c r="AA70" s="2" t="inlineStr"/>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr"/>
+      <c r="AE70" s="2" t="inlineStr"/>
+      <c r="AF70" s="2" t="inlineStr"/>
+      <c r="AG70" s="2" t="inlineStr"/>
+      <c r="AH70" s="2" t="inlineStr"/>
+      <c r="AI70" s="2" t="inlineStr"/>
+      <c r="AJ70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>45cca7fbaa3e41d5</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>85060feb5c496fb103bc90e5d86a4c227292d3b19db5f0ee6530b90f27040947</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>72080</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>0.806688</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>0.11628552321981422</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:02:40.119068Z</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr"/>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="AA71" s="2" t="inlineStr"/>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr"/>
+      <c r="AE71" s="2" t="inlineStr"/>
+      <c r="AF71" s="2" t="inlineStr"/>
+      <c r="AG71" s="2" t="inlineStr"/>
+      <c r="AH71" s="2" t="inlineStr"/>
+      <c r="AI71" s="2" t="inlineStr"/>
+      <c r="AJ71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>4c59e9fd7279468d</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>546b7ddc40d2d88d6d3595e5bcb1db940cf1ce399adcf006017b934a421d97f9</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>72079</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>0.500156</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>0.04970554954954953</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:10:41.164172Z</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr"/>
+      <c r="W72" s="2" t="inlineStr"/>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr"/>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr"/>
+      <c r="AE72" s="2" t="inlineStr"/>
+      <c r="AF72" s="2" t="inlineStr"/>
+      <c r="AG72" s="2" t="inlineStr"/>
+      <c r="AH72" s="2" t="inlineStr"/>
+      <c r="AI72" s="2" t="inlineStr"/>
+      <c r="AJ72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>4ee58e1aeebb437b</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>546b7ddc40d2d88d6d3595e5bcb1db940cf1ce399adcf006017b934a421d97f9</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>71970</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>0.6589</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>0.06873606557377054</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:10:41.974128Z</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr"/>
+      <c r="W73" s="2" t="inlineStr"/>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr"/>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr"/>
+      <c r="AE73" s="2" t="inlineStr"/>
+      <c r="AF73" s="2" t="inlineStr"/>
+      <c r="AG73" s="2" t="inlineStr"/>
+      <c r="AH73" s="2" t="inlineStr"/>
+      <c r="AI73" s="2" t="inlineStr"/>
+      <c r="AJ73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>facb2f5b46854896</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>546b7ddc40d2d88d6d3595e5bcb1db940cf1ce399adcf006017b934a421d97f9</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>72080</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>0.806464</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>0.11606152321981422</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:10:42.787518Z</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr"/>
+      <c r="W74" s="2" t="inlineStr"/>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr"/>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr"/>
+      <c r="AE74" s="2" t="inlineStr"/>
+      <c r="AF74" s="2" t="inlineStr"/>
+      <c r="AG74" s="2" t="inlineStr"/>
+      <c r="AH74" s="2" t="inlineStr"/>
+      <c r="AI74" s="2" t="inlineStr"/>
+      <c r="AJ74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>f253170856d5498a</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>548c08ed9b6099f179bd63a4381c3db833823e0a8e4abc4ee88c59d6bc6dba02</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>72079</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>0.500213</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>0.049762549549549506</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:18.721759Z</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr"/>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr"/>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr"/>
+      <c r="AE75" s="2" t="inlineStr"/>
+      <c r="AF75" s="2" t="inlineStr"/>
+      <c r="AG75" s="2" t="inlineStr"/>
+      <c r="AH75" s="2" t="inlineStr"/>
+      <c r="AI75" s="2" t="inlineStr"/>
+      <c r="AJ75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>a07d879201954f44</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>548c08ed9b6099f179bd63a4381c3db833823e0a8e4abc4ee88c59d6bc6dba02</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>71970</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>0.658692</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>0.11952149308755766</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:19.949179Z</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr"/>
+      <c r="W76" s="2" t="inlineStr"/>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr"/>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr"/>
+      <c r="AE76" s="2" t="inlineStr"/>
+      <c r="AF76" s="2" t="inlineStr"/>
+      <c r="AG76" s="2" t="inlineStr"/>
+      <c r="AH76" s="2" t="inlineStr"/>
+      <c r="AI76" s="2" t="inlineStr"/>
+      <c r="AJ76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2f4ee70c41a64c6a</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>548c08ed9b6099f179bd63a4381c3db833823e0a8e4abc4ee88c59d6bc6dba02</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>72080</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>0.80623</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>0.11582752321981427</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:20.857492Z</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr"/>
+      <c r="W77" s="2" t="inlineStr"/>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr"/>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr"/>
+      <c r="AE77" s="2" t="inlineStr"/>
+      <c r="AF77" s="2" t="inlineStr"/>
+      <c r="AG77" s="2" t="inlineStr"/>
+      <c r="AH77" s="2" t="inlineStr"/>
+      <c r="AI77" s="2" t="inlineStr"/>
+      <c r="AJ77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>cb0d595904bb4cb8</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>548c08ed9b6099f179bd63a4381c3db833823e0a8e4abc4ee88c59d6bc6dba02</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>70575</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>0.528651</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>0.07820054954954947</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:21.649402Z</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr"/>
+      <c r="W78" s="2" t="inlineStr"/>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Z78" s="2" t="inlineStr"/>
+      <c r="AA78" s="2" t="inlineStr"/>
+      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr"/>
+      <c r="AE78" s="2" t="inlineStr"/>
+      <c r="AF78" s="2" t="inlineStr"/>
+      <c r="AG78" s="2" t="inlineStr"/>
+      <c r="AH78" s="2" t="inlineStr"/>
+      <c r="AI78" s="2" t="inlineStr"/>
+      <c r="AJ78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>9fedb01bea494a24</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>548c08ed9b6099f179bd63a4381c3db833823e0a8e4abc4ee88c59d6bc6dba02</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>70648</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>0.611731</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>0.211731</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:22.425948Z</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr"/>
+      <c r="W79" s="2" t="inlineStr"/>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr"/>
+      <c r="Z79" s="2" t="inlineStr"/>
+      <c r="AA79" s="2" t="inlineStr"/>
+      <c r="AB79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr"/>
+      <c r="AE79" s="2" t="inlineStr"/>
+      <c r="AF79" s="2" t="inlineStr"/>
+      <c r="AG79" s="2" t="inlineStr"/>
+      <c r="AH79" s="2" t="inlineStr"/>
+      <c r="AI79" s="2" t="inlineStr"/>
+      <c r="AJ79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>87521710d76d4f78</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>548c08ed9b6099f179bd63a4381c3db833823e0a8e4abc4ee88c59d6bc6dba02</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>0.558681</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>0.009131450450450496</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:23.221752Z</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr"/>
+      <c r="W80" s="2" t="inlineStr"/>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr"/>
+      <c r="Z80" s="2" t="inlineStr"/>
+      <c r="AA80" s="2" t="inlineStr"/>
+      <c r="AB80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr"/>
+      <c r="AE80" s="2" t="inlineStr"/>
+      <c r="AF80" s="2" t="inlineStr"/>
+      <c r="AG80" s="2" t="inlineStr"/>
+      <c r="AH80" s="2" t="inlineStr"/>
+      <c r="AI80" s="2" t="inlineStr"/>
+      <c r="AJ80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>ef010b12f7aa4d76</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>72079</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>0.500216</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>0.04976554954954948</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:08.611098Z</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr"/>
+      <c r="W81" s="2" t="inlineStr"/>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr"/>
+      <c r="Z81" s="2" t="inlineStr"/>
+      <c r="AA81" s="2" t="inlineStr"/>
+      <c r="AB81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr"/>
+      <c r="AE81" s="2" t="inlineStr"/>
+      <c r="AF81" s="2" t="inlineStr"/>
+      <c r="AG81" s="2" t="inlineStr"/>
+      <c r="AH81" s="2" t="inlineStr"/>
+      <c r="AI81" s="2" t="inlineStr"/>
+      <c r="AJ81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>7998ca79d595462e</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>71970</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>0.658681</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>0.12816456807511734</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:09.196950Z</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr"/>
+      <c r="W82" s="2" t="inlineStr"/>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr"/>
+      <c r="Z82" s="2" t="inlineStr"/>
+      <c r="AA82" s="2" t="inlineStr"/>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr"/>
+      <c r="AE82" s="2" t="inlineStr"/>
+      <c r="AF82" s="2" t="inlineStr"/>
+      <c r="AG82" s="2" t="inlineStr"/>
+      <c r="AH82" s="2" t="inlineStr"/>
+      <c r="AI82" s="2" t="inlineStr"/>
+      <c r="AJ82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>dcb4bd4bf91946cb</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>72080</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>0.806217</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>0.11581452321981422</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:09.769926Z</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr"/>
+      <c r="W83" s="2" t="inlineStr"/>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr"/>
+      <c r="Z83" s="2" t="inlineStr"/>
+      <c r="AA83" s="2" t="inlineStr"/>
+      <c r="AB83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr"/>
+      <c r="AE83" s="2" t="inlineStr"/>
+      <c r="AF83" s="2" t="inlineStr"/>
+      <c r="AG83" s="2" t="inlineStr"/>
+      <c r="AH83" s="2" t="inlineStr"/>
+      <c r="AI83" s="2" t="inlineStr"/>
+      <c r="AJ83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>a89e3246ddfd408a</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>70575</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>0.528647</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>0.07819654954954947</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:10.316562Z</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr"/>
+      <c r="W84" s="2" t="inlineStr"/>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr"/>
+      <c r="Z84" s="2" t="inlineStr"/>
+      <c r="AA84" s="2" t="inlineStr"/>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr"/>
+      <c r="AE84" s="2" t="inlineStr"/>
+      <c r="AF84" s="2" t="inlineStr"/>
+      <c r="AG84" s="2" t="inlineStr"/>
+      <c r="AH84" s="2" t="inlineStr"/>
+      <c r="AI84" s="2" t="inlineStr"/>
+      <c r="AJ84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>39be0c4275e14a8f</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>70648</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>0.611725</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>0.21172499999999994</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:10.870839Z</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr"/>
+      <c r="W85" s="2" t="inlineStr"/>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr"/>
+      <c r="Z85" s="2" t="inlineStr"/>
+      <c r="AA85" s="2" t="inlineStr"/>
+      <c r="AB85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr"/>
+      <c r="AE85" s="2" t="inlineStr"/>
+      <c r="AF85" s="2" t="inlineStr"/>
+      <c r="AG85" s="2" t="inlineStr"/>
+      <c r="AH85" s="2" t="inlineStr"/>
+      <c r="AI85" s="2" t="inlineStr"/>
+      <c r="AJ85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>5e9d0736373b4002</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>0.558677</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>-0.0007943656387665587</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:11.700160Z</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr"/>
+      <c r="W86" s="2" t="inlineStr"/>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr"/>
+      <c r="Z86" s="2" t="inlineStr"/>
+      <c r="AA86" s="2" t="inlineStr"/>
+      <c r="AB86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr"/>
+      <c r="AE86" s="2" t="inlineStr"/>
+      <c r="AF86" s="2" t="inlineStr"/>
+      <c r="AG86" s="2" t="inlineStr"/>
+      <c r="AH86" s="2" t="inlineStr"/>
+      <c r="AI86" s="2" t="inlineStr"/>
+      <c r="AJ86" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ66"/>
+  <autoFilter ref="A1:AJ86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/dota2-tiered-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ86"/>
+  <dimension ref="A1:AJ97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8960,14 +8960,34 @@
       <c r="W81" s="2" t="inlineStr"/>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y81" s="2" t="inlineStr"/>
-      <c r="Z81" s="2" t="inlineStr"/>
-      <c r="AA81" s="2" t="inlineStr"/>
-      <c r="AB81" s="2" t="inlineStr"/>
-      <c r="AC81" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>0.450000</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>-0.000450</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1.2200</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:17:02.307848Z</t>
+        </is>
+      </c>
       <c r="AD81" s="2" t="inlineStr"/>
       <c r="AE81" s="2" t="inlineStr"/>
       <c r="AF81" s="2" t="inlineStr"/>
@@ -9062,14 +9082,34 @@
       <c r="W82" s="2" t="inlineStr"/>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y82" s="2" t="inlineStr"/>
-      <c r="Z82" s="2" t="inlineStr"/>
-      <c r="AA82" s="2" t="inlineStr"/>
-      <c r="AB82" s="2" t="inlineStr"/>
-      <c r="AC82" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>0.530000</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>-0.000516</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>-1.7500</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:50:43.408680Z</t>
+        </is>
+      </c>
       <c r="AD82" s="2" t="inlineStr"/>
       <c r="AE82" s="2" t="inlineStr"/>
       <c r="AF82" s="2" t="inlineStr"/>
@@ -9486,8 +9526,1130 @@
       <c r="AI86" s="2" t="inlineStr"/>
       <c r="AJ86" s="2" t="inlineStr"/>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>be19630a29004a24</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>ba2789968b6b878222d506d0a92e1f19b7add9d1842603ccf61abf88d6358248</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>72080</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>0.805806</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>0.13583900330033005</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:14.376997Z</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr"/>
+      <c r="W87" s="2" t="inlineStr"/>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr"/>
+      <c r="Z87" s="2" t="inlineStr"/>
+      <c r="AA87" s="2" t="inlineStr"/>
+      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr"/>
+      <c r="AE87" s="2" t="inlineStr"/>
+      <c r="AF87" s="2" t="inlineStr"/>
+      <c r="AG87" s="2" t="inlineStr"/>
+      <c r="AH87" s="2" t="inlineStr"/>
+      <c r="AI87" s="2" t="inlineStr"/>
+      <c r="AJ87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>51a07a9a46724fe6</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>ba2789968b6b878222d506d0a92e1f19b7add9d1842603ccf61abf88d6358248</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>70575</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>0.528546</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>0.0880173656387665</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:14.941264Z</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr"/>
+      <c r="W88" s="2" t="inlineStr"/>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Z88" s="2" t="inlineStr"/>
+      <c r="AA88" s="2" t="inlineStr"/>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr"/>
+      <c r="AE88" s="2" t="inlineStr"/>
+      <c r="AF88" s="2" t="inlineStr"/>
+      <c r="AG88" s="2" t="inlineStr"/>
+      <c r="AH88" s="2" t="inlineStr"/>
+      <c r="AI88" s="2" t="inlineStr"/>
+      <c r="AJ88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>bffe8771fd694fab</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>ba2789968b6b878222d506d0a92e1f19b7add9d1842603ccf61abf88d6358248</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>70648</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>0.611532</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>0.21153199999999994</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:15.642613Z</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr"/>
+      <c r="W89" s="2" t="inlineStr"/>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr"/>
+      <c r="Z89" s="2" t="inlineStr"/>
+      <c r="AA89" s="2" t="inlineStr"/>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr"/>
+      <c r="AE89" s="2" t="inlineStr"/>
+      <c r="AF89" s="2" t="inlineStr"/>
+      <c r="AG89" s="2" t="inlineStr"/>
+      <c r="AH89" s="2" t="inlineStr"/>
+      <c r="AI89" s="2" t="inlineStr"/>
+      <c r="AJ89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>c751b80b07a94ef9</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>ba2789968b6b878222d506d0a92e1f19b7add9d1842603ccf61abf88d6358248</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>0.558528</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>-0.021303932773109158</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:16.322159Z</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr"/>
+      <c r="W90" s="2" t="inlineStr"/>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr"/>
+      <c r="Z90" s="2" t="inlineStr"/>
+      <c r="AA90" s="2" t="inlineStr"/>
+      <c r="AB90" s="2" t="inlineStr"/>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr"/>
+      <c r="AE90" s="2" t="inlineStr"/>
+      <c r="AF90" s="2" t="inlineStr"/>
+      <c r="AG90" s="2" t="inlineStr"/>
+      <c r="AH90" s="2" t="inlineStr"/>
+      <c r="AI90" s="2" t="inlineStr"/>
+      <c r="AJ90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>a7633b0b5a674194</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>72080</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>0.805779</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>0.13581200330033005</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:27.725458Z</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr"/>
+      <c r="W91" s="2" t="inlineStr"/>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr"/>
+      <c r="Z91" s="2" t="inlineStr"/>
+      <c r="AA91" s="2" t="inlineStr"/>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr"/>
+      <c r="AE91" s="2" t="inlineStr"/>
+      <c r="AF91" s="2" t="inlineStr"/>
+      <c r="AG91" s="2" t="inlineStr"/>
+      <c r="AH91" s="2" t="inlineStr"/>
+      <c r="AI91" s="2" t="inlineStr"/>
+      <c r="AJ91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>743119289c6d428e</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>70575</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>0.52854</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>0.08801136563876655</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:28.597199Z</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr"/>
+      <c r="W92" s="2" t="inlineStr"/>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr"/>
+      <c r="Z92" s="2" t="inlineStr"/>
+      <c r="AA92" s="2" t="inlineStr"/>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr"/>
+      <c r="AE92" s="2" t="inlineStr"/>
+      <c r="AF92" s="2" t="inlineStr"/>
+      <c r="AG92" s="2" t="inlineStr"/>
+      <c r="AH92" s="2" t="inlineStr"/>
+      <c r="AI92" s="2" t="inlineStr"/>
+      <c r="AJ92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>9a23090a274047fa</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>70648</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>0.611519</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>0.211519</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:29.187069Z</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr"/>
+      <c r="W93" s="2" t="inlineStr"/>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr"/>
+      <c r="Z93" s="2" t="inlineStr"/>
+      <c r="AA93" s="2" t="inlineStr"/>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr"/>
+      <c r="AE93" s="2" t="inlineStr"/>
+      <c r="AF93" s="2" t="inlineStr"/>
+      <c r="AG93" s="2" t="inlineStr"/>
+      <c r="AH93" s="2" t="inlineStr"/>
+      <c r="AI93" s="2" t="inlineStr"/>
+      <c r="AJ93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>8faaa481e3964ea5</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>0.558518</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>-0.021313932773109223</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:30.519412Z</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr"/>
+      <c r="W94" s="2" t="inlineStr"/>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr"/>
+      <c r="Z94" s="2" t="inlineStr"/>
+      <c r="AA94" s="2" t="inlineStr"/>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr"/>
+      <c r="AE94" s="2" t="inlineStr"/>
+      <c r="AF94" s="2" t="inlineStr"/>
+      <c r="AG94" s="2" t="inlineStr"/>
+      <c r="AH94" s="2" t="inlineStr"/>
+      <c r="AI94" s="2" t="inlineStr"/>
+      <c r="AJ94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>0f24cc9e66a341a1</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>70575</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>0.528031</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>0.09884645064377684</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:07.743708Z</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr"/>
+      <c r="W95" s="2" t="inlineStr"/>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr"/>
+      <c r="Z95" s="2" t="inlineStr"/>
+      <c r="AA95" s="2" t="inlineStr"/>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr"/>
+      <c r="AE95" s="2" t="inlineStr"/>
+      <c r="AF95" s="2" t="inlineStr"/>
+      <c r="AG95" s="2" t="inlineStr"/>
+      <c r="AH95" s="2" t="inlineStr"/>
+      <c r="AI95" s="2" t="inlineStr"/>
+      <c r="AJ95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>05e6ad4cd75d4490</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>70648</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>0.611634</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>0.211634</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:08.266131Z</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr"/>
+      <c r="W96" s="2" t="inlineStr"/>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr"/>
+      <c r="Z96" s="2" t="inlineStr"/>
+      <c r="AA96" s="2" t="inlineStr"/>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr"/>
+      <c r="AE96" s="2" t="inlineStr"/>
+      <c r="AF96" s="2" t="inlineStr"/>
+      <c r="AG96" s="2" t="inlineStr"/>
+      <c r="AH96" s="2" t="inlineStr"/>
+      <c r="AI96" s="2" t="inlineStr"/>
+      <c r="AJ96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>250e90547f6941f8</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>0.557963</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>-0.012852450643776825</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:08.986800Z</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="2" t="inlineStr"/>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr"/>
+      <c r="Z97" s="2" t="inlineStr"/>
+      <c r="AA97" s="2" t="inlineStr"/>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr"/>
+      <c r="AE97" s="2" t="inlineStr"/>
+      <c r="AF97" s="2" t="inlineStr"/>
+      <c r="AG97" s="2" t="inlineStr"/>
+      <c r="AH97" s="2" t="inlineStr"/>
+      <c r="AI97" s="2" t="inlineStr"/>
+      <c r="AJ97" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ86"/>
+  <autoFilter ref="A1:AJ97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ97"/>
+  <dimension ref="A1:AJ127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -10020,14 +10020,34 @@
       <c r="W91" s="2" t="inlineStr"/>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y91" s="2" t="inlineStr"/>
-      <c r="Z91" s="2" t="inlineStr"/>
-      <c r="AA91" s="2" t="inlineStr"/>
-      <c r="AB91" s="2" t="inlineStr"/>
-      <c r="AC91" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>0.670000</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>0.000033</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0.9852</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:04.650174Z</t>
+        </is>
+      </c>
       <c r="AD91" s="2" t="inlineStr"/>
       <c r="AE91" s="2" t="inlineStr"/>
       <c r="AF91" s="2" t="inlineStr"/>
@@ -10648,8 +10668,3144 @@
       <c r="AI97" s="2" t="inlineStr"/>
       <c r="AJ97" s="2" t="inlineStr"/>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>575dc948cae341cc</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>bcd519f52f5e721482ed7278f0d1f8595eb579735f62ade6d9901bb399c5adc6</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>70575</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>0.527614</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>0.09842945064377684</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:40.611953Z</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr"/>
+      <c r="W98" s="2" t="inlineStr"/>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr"/>
+      <c r="Z98" s="2" t="inlineStr"/>
+      <c r="AA98" s="2" t="inlineStr"/>
+      <c r="AB98" s="2" t="inlineStr"/>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr"/>
+      <c r="AE98" s="2" t="inlineStr"/>
+      <c r="AF98" s="2" t="inlineStr"/>
+      <c r="AG98" s="2" t="inlineStr"/>
+      <c r="AH98" s="2" t="inlineStr"/>
+      <c r="AI98" s="2" t="inlineStr"/>
+      <c r="AJ98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01ccde158af04ef1</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>bcd519f52f5e721482ed7278f0d1f8595eb579735f62ade6d9901bb399c5adc6</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>70648</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>0.611574</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>0.21157399999999993</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:41.132772Z</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr"/>
+      <c r="W99" s="2" t="inlineStr"/>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr"/>
+      <c r="Z99" s="2" t="inlineStr"/>
+      <c r="AA99" s="2" t="inlineStr"/>
+      <c r="AB99" s="2" t="inlineStr"/>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr"/>
+      <c r="AE99" s="2" t="inlineStr"/>
+      <c r="AF99" s="2" t="inlineStr"/>
+      <c r="AG99" s="2" t="inlineStr"/>
+      <c r="AH99" s="2" t="inlineStr"/>
+      <c r="AI99" s="2" t="inlineStr"/>
+      <c r="AJ99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>51199650d8f64516</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>bcd519f52f5e721482ed7278f0d1f8595eb579735f62ade6d9901bb399c5adc6</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>0.557487</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>-0.013328450643776857</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:41.669128Z</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr"/>
+      <c r="W100" s="2" t="inlineStr"/>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr"/>
+      <c r="Z100" s="2" t="inlineStr"/>
+      <c r="AA100" s="2" t="inlineStr"/>
+      <c r="AB100" s="2" t="inlineStr"/>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr"/>
+      <c r="AE100" s="2" t="inlineStr"/>
+      <c r="AF100" s="2" t="inlineStr"/>
+      <c r="AG100" s="2" t="inlineStr"/>
+      <c r="AH100" s="2" t="inlineStr"/>
+      <c r="AI100" s="2" t="inlineStr"/>
+      <c r="AJ100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>7534415721234621</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>fe93a59dffe853e63cc2242ea366e0c3beef0e6a397ff603085d1a5881cecab0</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>70575</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>0.527545</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>0.08701636563876658</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:47.369737Z</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr"/>
+      <c r="W101" s="2" t="inlineStr"/>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr"/>
+      <c r="Z101" s="2" t="inlineStr"/>
+      <c r="AA101" s="2" t="inlineStr"/>
+      <c r="AB101" s="2" t="inlineStr"/>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr"/>
+      <c r="AE101" s="2" t="inlineStr"/>
+      <c r="AF101" s="2" t="inlineStr"/>
+      <c r="AG101" s="2" t="inlineStr"/>
+      <c r="AH101" s="2" t="inlineStr"/>
+      <c r="AI101" s="2" t="inlineStr"/>
+      <c r="AJ101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>b28309ee5f5c4b9d</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>fe93a59dffe853e63cc2242ea366e0c3beef0e6a397ff603085d1a5881cecab0</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>70648</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>0.611442</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>0.19127393277310928</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:47.895830Z</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr"/>
+      <c r="W102" s="2" t="inlineStr"/>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr"/>
+      <c r="Z102" s="2" t="inlineStr"/>
+      <c r="AA102" s="2" t="inlineStr"/>
+      <c r="AB102" s="2" t="inlineStr"/>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr"/>
+      <c r="AE102" s="2" t="inlineStr"/>
+      <c r="AF102" s="2" t="inlineStr"/>
+      <c r="AG102" s="2" t="inlineStr"/>
+      <c r="AH102" s="2" t="inlineStr"/>
+      <c r="AI102" s="2" t="inlineStr"/>
+      <c r="AJ102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>8b28fa6b9dae4e89</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>fe93a59dffe853e63cc2242ea366e0c3beef0e6a397ff603085d1a5881cecab0</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>0.557386</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>-0.022445932773109134</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:48.561837Z</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr"/>
+      <c r="W103" s="2" t="inlineStr"/>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr"/>
+      <c r="Z103" s="2" t="inlineStr"/>
+      <c r="AA103" s="2" t="inlineStr"/>
+      <c r="AB103" s="2" t="inlineStr"/>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr"/>
+      <c r="AE103" s="2" t="inlineStr"/>
+      <c r="AF103" s="2" t="inlineStr"/>
+      <c r="AG103" s="2" t="inlineStr"/>
+      <c r="AH103" s="2" t="inlineStr"/>
+      <c r="AI103" s="2" t="inlineStr"/>
+      <c r="AJ103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>95bbbad7ee19494d</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>70575</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>0.527212</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>0.08668336563876655</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:35.411288Z</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr"/>
+      <c r="W104" s="2" t="inlineStr"/>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr"/>
+      <c r="AA104" s="2" t="inlineStr"/>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:55:17.006068Z</t>
+        </is>
+      </c>
+      <c r="AD104" s="2" t="inlineStr"/>
+      <c r="AE104" s="2" t="inlineStr"/>
+      <c r="AF104" s="2" t="inlineStr"/>
+      <c r="AG104" s="2" t="inlineStr"/>
+      <c r="AH104" s="2" t="inlineStr"/>
+      <c r="AI104" s="2" t="inlineStr"/>
+      <c r="AJ104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>13112f1ba544477d</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>70648</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>0.61125</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr"/>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>0.18206545064377677</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:35.868255Z</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr"/>
+      <c r="W105" s="2" t="inlineStr"/>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr"/>
+      <c r="AA105" s="2" t="inlineStr"/>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>1.9950</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:55:18.636784Z</t>
+        </is>
+      </c>
+      <c r="AD105" s="2" t="inlineStr"/>
+      <c r="AE105" s="2" t="inlineStr"/>
+      <c r="AF105" s="2" t="inlineStr"/>
+      <c r="AG105" s="2" t="inlineStr"/>
+      <c r="AH105" s="2" t="inlineStr"/>
+      <c r="AI105" s="2" t="inlineStr"/>
+      <c r="AJ105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>69d59b43fca643c5</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>0.55707</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr"/>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>-0.022761932773109228</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:36.336119Z</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr"/>
+      <c r="W106" s="2" t="inlineStr"/>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr"/>
+      <c r="AA106" s="2" t="inlineStr"/>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:00:37.901256Z</t>
+        </is>
+      </c>
+      <c r="AD106" s="2" t="inlineStr"/>
+      <c r="AE106" s="2" t="inlineStr"/>
+      <c r="AF106" s="2" t="inlineStr"/>
+      <c r="AG106" s="2" t="inlineStr"/>
+      <c r="AH106" s="2" t="inlineStr"/>
+      <c r="AI106" s="2" t="inlineStr"/>
+      <c r="AJ106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>e5472c37d39f4459</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>a5bd8362c1f057f2ff2da18f9897515a046c0c977de5f35846b085bd59815e4a</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>71682</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>0.656211</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr"/>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>0.0562109999999999</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:13.032355Z</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr"/>
+      <c r="W107" s="2" t="inlineStr"/>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr"/>
+      <c r="Z107" s="2" t="inlineStr"/>
+      <c r="AA107" s="2" t="inlineStr"/>
+      <c r="AB107" s="2" t="inlineStr"/>
+      <c r="AC107" s="2" t="inlineStr"/>
+      <c r="AD107" s="2" t="inlineStr"/>
+      <c r="AE107" s="2" t="inlineStr"/>
+      <c r="AF107" s="2" t="inlineStr"/>
+      <c r="AG107" s="2" t="inlineStr"/>
+      <c r="AH107" s="2" t="inlineStr"/>
+      <c r="AI107" s="2" t="inlineStr"/>
+      <c r="AJ107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>c3a50eae664b418f</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>a5bd8362c1f057f2ff2da18f9897515a046c0c977de5f35846b085bd59815e4a</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>71775</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>0.520478</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr"/>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>0.030281921568627468</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:13.531459Z</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr"/>
+      <c r="W108" s="2" t="inlineStr"/>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr"/>
+      <c r="Z108" s="2" t="inlineStr"/>
+      <c r="AA108" s="2" t="inlineStr"/>
+      <c r="AB108" s="2" t="inlineStr"/>
+      <c r="AC108" s="2" t="inlineStr"/>
+      <c r="AD108" s="2" t="inlineStr"/>
+      <c r="AE108" s="2" t="inlineStr"/>
+      <c r="AF108" s="2" t="inlineStr"/>
+      <c r="AG108" s="2" t="inlineStr"/>
+      <c r="AH108" s="2" t="inlineStr"/>
+      <c r="AI108" s="2" t="inlineStr"/>
+      <c r="AJ108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>de5ea6b4c5ef4709</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>a5bd8362c1f057f2ff2da18f9897515a046c0c977de5f35846b085bd59815e4a</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>72081</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>0.602889</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr"/>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>-0.05697494557823135</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:14.645119Z</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr"/>
+      <c r="W109" s="2" t="inlineStr"/>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr"/>
+      <c r="Z109" s="2" t="inlineStr"/>
+      <c r="AA109" s="2" t="inlineStr"/>
+      <c r="AB109" s="2" t="inlineStr"/>
+      <c r="AC109" s="2" t="inlineStr"/>
+      <c r="AD109" s="2" t="inlineStr"/>
+      <c r="AE109" s="2" t="inlineStr"/>
+      <c r="AF109" s="2" t="inlineStr"/>
+      <c r="AG109" s="2" t="inlineStr"/>
+      <c r="AH109" s="2" t="inlineStr"/>
+      <c r="AI109" s="2" t="inlineStr"/>
+      <c r="AJ109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>43dd47d9eae34508</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>71682</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>0.655357</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr"/>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>0.08454154935622316</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:28.583196Z</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr"/>
+      <c r="W110" s="2" t="inlineStr"/>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>0.570000</t>
+        </is>
+      </c>
+      <c r="AA110" s="2" t="inlineStr">
+        <is>
+          <t>-0.000815</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
+          <t>1.3158</t>
+        </is>
+      </c>
+      <c r="AC110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:13:03.062038Z</t>
+        </is>
+      </c>
+      <c r="AD110" s="2" t="inlineStr"/>
+      <c r="AE110" s="2" t="inlineStr"/>
+      <c r="AF110" s="2" t="inlineStr"/>
+      <c r="AG110" s="2" t="inlineStr"/>
+      <c r="AH110" s="2" t="inlineStr"/>
+      <c r="AI110" s="2" t="inlineStr"/>
+      <c r="AJ110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>0420ec074e8549c3</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>71775</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>0.534325</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr"/>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>0.12448893442622955</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:29.205515Z</t>
+        </is>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr"/>
+      <c r="W111" s="2" t="inlineStr"/>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr"/>
+      <c r="Z111" s="2" t="inlineStr"/>
+      <c r="AA111" s="2" t="inlineStr"/>
+      <c r="AB111" s="2" t="inlineStr"/>
+      <c r="AC111" s="2" t="inlineStr"/>
+      <c r="AD111" s="2" t="inlineStr"/>
+      <c r="AE111" s="2" t="inlineStr"/>
+      <c r="AF111" s="2" t="inlineStr"/>
+      <c r="AG111" s="2" t="inlineStr"/>
+      <c r="AH111" s="2" t="inlineStr"/>
+      <c r="AI111" s="2" t="inlineStr"/>
+      <c r="AJ111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>a0c1d3c4e66143f1</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>71907</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>0.660088</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>-0.020423182108626148</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:30.190895Z</t>
+        </is>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr"/>
+      <c r="W112" s="2" t="inlineStr"/>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr"/>
+      <c r="Z112" s="2" t="inlineStr"/>
+      <c r="AA112" s="2" t="inlineStr"/>
+      <c r="AB112" s="2" t="inlineStr"/>
+      <c r="AC112" s="2" t="inlineStr"/>
+      <c r="AD112" s="2" t="inlineStr"/>
+      <c r="AE112" s="2" t="inlineStr"/>
+      <c r="AF112" s="2" t="inlineStr"/>
+      <c r="AG112" s="2" t="inlineStr"/>
+      <c r="AH112" s="2" t="inlineStr"/>
+      <c r="AI112" s="2" t="inlineStr"/>
+      <c r="AJ112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>28eff5022dc64634</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>72081</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>0.602742</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr"/>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>0.012578065573770503</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:30.830987Z</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr"/>
+      <c r="W113" s="2" t="inlineStr"/>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr"/>
+      <c r="Z113" s="2" t="inlineStr"/>
+      <c r="AA113" s="2" t="inlineStr"/>
+      <c r="AB113" s="2" t="inlineStr"/>
+      <c r="AC113" s="2" t="inlineStr"/>
+      <c r="AD113" s="2" t="inlineStr"/>
+      <c r="AE113" s="2" t="inlineStr"/>
+      <c r="AF113" s="2" t="inlineStr"/>
+      <c r="AG113" s="2" t="inlineStr"/>
+      <c r="AH113" s="2" t="inlineStr"/>
+      <c r="AI113" s="2" t="inlineStr"/>
+      <c r="AJ113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>10abe9e20ad14e53</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>72729</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>0.622858</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>0.24262986311787071</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:31.608152Z</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="2" t="inlineStr"/>
+      <c r="W114" s="2" t="inlineStr"/>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y114" s="2" t="inlineStr"/>
+      <c r="Z114" s="2" t="inlineStr"/>
+      <c r="AA114" s="2" t="inlineStr"/>
+      <c r="AB114" s="2" t="inlineStr"/>
+      <c r="AC114" s="2" t="inlineStr"/>
+      <c r="AD114" s="2" t="inlineStr"/>
+      <c r="AE114" s="2" t="inlineStr"/>
+      <c r="AF114" s="2" t="inlineStr"/>
+      <c r="AG114" s="2" t="inlineStr"/>
+      <c r="AH114" s="2" t="inlineStr"/>
+      <c r="AI114" s="2" t="inlineStr"/>
+      <c r="AJ114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>4961c8d69c784b25</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>71775</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>0.534269</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr"/>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>0.13426899999999997</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:20.860338Z</t>
+        </is>
+      </c>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr"/>
+      <c r="W115" s="2" t="inlineStr"/>
+      <c r="X115" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y115" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z115" s="2" t="inlineStr">
+        <is>
+          <t>0.400000</t>
+        </is>
+      </c>
+      <c r="AA115" s="2" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="AB115" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:18:45.633729Z</t>
+        </is>
+      </c>
+      <c r="AD115" s="2" t="inlineStr"/>
+      <c r="AE115" s="2" t="inlineStr"/>
+      <c r="AF115" s="2" t="inlineStr"/>
+      <c r="AG115" s="2" t="inlineStr"/>
+      <c r="AH115" s="2" t="inlineStr"/>
+      <c r="AI115" s="2" t="inlineStr"/>
+      <c r="AJ115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>3ad69c4c879a429d</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>71907</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>0.659933</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>-0.020578182108626164</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:22.184044Z</t>
+        </is>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr"/>
+      <c r="W116" s="2" t="inlineStr"/>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr"/>
+      <c r="Z116" s="2" t="inlineStr"/>
+      <c r="AA116" s="2" t="inlineStr"/>
+      <c r="AB116" s="2" t="inlineStr"/>
+      <c r="AC116" s="2" t="inlineStr"/>
+      <c r="AD116" s="2" t="inlineStr"/>
+      <c r="AE116" s="2" t="inlineStr"/>
+      <c r="AF116" s="2" t="inlineStr"/>
+      <c r="AG116" s="2" t="inlineStr"/>
+      <c r="AH116" s="2" t="inlineStr"/>
+      <c r="AI116" s="2" t="inlineStr"/>
+      <c r="AJ116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>9b13ea9ba2c5426f</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>72081</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>0.602651</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr"/>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr"/>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>0.002650999999999959</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:22.691108Z</t>
+        </is>
+      </c>
+      <c r="S117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr"/>
+      <c r="W117" s="2" t="inlineStr"/>
+      <c r="X117" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y117" s="2" t="inlineStr"/>
+      <c r="Z117" s="2" t="inlineStr"/>
+      <c r="AA117" s="2" t="inlineStr"/>
+      <c r="AB117" s="2" t="inlineStr"/>
+      <c r="AC117" s="2" t="inlineStr"/>
+      <c r="AD117" s="2" t="inlineStr"/>
+      <c r="AE117" s="2" t="inlineStr"/>
+      <c r="AF117" s="2" t="inlineStr"/>
+      <c r="AG117" s="2" t="inlineStr"/>
+      <c r="AH117" s="2" t="inlineStr"/>
+      <c r="AI117" s="2" t="inlineStr"/>
+      <c r="AJ117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>76a8e6f3c0dd4329</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>72729</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>0.622731</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>0.222731</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:24.357021Z</t>
+        </is>
+      </c>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr"/>
+      <c r="W118" s="2" t="inlineStr"/>
+      <c r="X118" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y118" s="2" t="inlineStr"/>
+      <c r="Z118" s="2" t="inlineStr"/>
+      <c r="AA118" s="2" t="inlineStr"/>
+      <c r="AB118" s="2" t="inlineStr"/>
+      <c r="AC118" s="2" t="inlineStr"/>
+      <c r="AD118" s="2" t="inlineStr"/>
+      <c r="AE118" s="2" t="inlineStr"/>
+      <c r="AF118" s="2" t="inlineStr"/>
+      <c r="AG118" s="2" t="inlineStr"/>
+      <c r="AH118" s="2" t="inlineStr"/>
+      <c r="AI118" s="2" t="inlineStr"/>
+      <c r="AJ118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>77805546ab28459d</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>007188172239d3dfb1106fac54f73170318b23e441cc93d6e8e709844ef5fc38</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>71907</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>0.659257</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr"/>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr"/>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>-0.021254182108626174</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:10.694583Z</t>
+        </is>
+      </c>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr"/>
+      <c r="W119" s="2" t="inlineStr"/>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr"/>
+      <c r="Z119" s="2" t="inlineStr"/>
+      <c r="AA119" s="2" t="inlineStr"/>
+      <c r="AB119" s="2" t="inlineStr"/>
+      <c r="AC119" s="2" t="inlineStr"/>
+      <c r="AD119" s="2" t="inlineStr"/>
+      <c r="AE119" s="2" t="inlineStr"/>
+      <c r="AF119" s="2" t="inlineStr"/>
+      <c r="AG119" s="2" t="inlineStr"/>
+      <c r="AH119" s="2" t="inlineStr"/>
+      <c r="AI119" s="2" t="inlineStr"/>
+      <c r="AJ119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>47688694030f4d1e</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>007188172239d3dfb1106fac54f73170318b23e441cc93d6e8e709844ef5fc38</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>72081</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>0.602039</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr"/>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>0.002038999999999902</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:11.248629Z</t>
+        </is>
+      </c>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr"/>
+      <c r="W120" s="2" t="inlineStr"/>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr"/>
+      <c r="Z120" s="2" t="inlineStr"/>
+      <c r="AA120" s="2" t="inlineStr"/>
+      <c r="AB120" s="2" t="inlineStr"/>
+      <c r="AC120" s="2" t="inlineStr"/>
+      <c r="AD120" s="2" t="inlineStr"/>
+      <c r="AE120" s="2" t="inlineStr"/>
+      <c r="AF120" s="2" t="inlineStr"/>
+      <c r="AG120" s="2" t="inlineStr"/>
+      <c r="AH120" s="2" t="inlineStr"/>
+      <c r="AI120" s="2" t="inlineStr"/>
+      <c r="AJ120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>9f5b19e8a7f342f0</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>007188172239d3dfb1106fac54f73170318b23e441cc93d6e8e709844ef5fc38</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>74328</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>0.536135</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr"/>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>-0.01341454954954946</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:11.841734Z</t>
+        </is>
+      </c>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr"/>
+      <c r="W121" s="2" t="inlineStr"/>
+      <c r="X121" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y121" s="2" t="inlineStr"/>
+      <c r="Z121" s="2" t="inlineStr"/>
+      <c r="AA121" s="2" t="inlineStr"/>
+      <c r="AB121" s="2" t="inlineStr"/>
+      <c r="AC121" s="2" t="inlineStr"/>
+      <c r="AD121" s="2" t="inlineStr"/>
+      <c r="AE121" s="2" t="inlineStr"/>
+      <c r="AF121" s="2" t="inlineStr"/>
+      <c r="AG121" s="2" t="inlineStr"/>
+      <c r="AH121" s="2" t="inlineStr"/>
+      <c r="AI121" s="2" t="inlineStr"/>
+      <c r="AJ121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>9415e37263ee4b64</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>007188172239d3dfb1106fac54f73170318b23e441cc93d6e8e709844ef5fc38</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>72729</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>0.622071</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr"/>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>0.24184286311787073</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:12.435406Z</t>
+        </is>
+      </c>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr"/>
+      <c r="W122" s="2" t="inlineStr"/>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y122" s="2" t="inlineStr"/>
+      <c r="Z122" s="2" t="inlineStr"/>
+      <c r="AA122" s="2" t="inlineStr"/>
+      <c r="AB122" s="2" t="inlineStr"/>
+      <c r="AC122" s="2" t="inlineStr"/>
+      <c r="AD122" s="2" t="inlineStr"/>
+      <c r="AE122" s="2" t="inlineStr"/>
+      <c r="AF122" s="2" t="inlineStr"/>
+      <c r="AG122" s="2" t="inlineStr"/>
+      <c r="AH122" s="2" t="inlineStr"/>
+      <c r="AI122" s="2" t="inlineStr"/>
+      <c r="AJ122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>55db13698a614757</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>007188172239d3dfb1106fac54f73170318b23e441cc93d6e8e709844ef5fc38</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>74329</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>0.654351</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr"/>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>0.2741228631178707</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:12.940691Z</t>
+        </is>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr"/>
+      <c r="W123" s="2" t="inlineStr"/>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr"/>
+      <c r="Z123" s="2" t="inlineStr"/>
+      <c r="AA123" s="2" t="inlineStr"/>
+      <c r="AB123" s="2" t="inlineStr"/>
+      <c r="AC123" s="2" t="inlineStr"/>
+      <c r="AD123" s="2" t="inlineStr"/>
+      <c r="AE123" s="2" t="inlineStr"/>
+      <c r="AF123" s="2" t="inlineStr"/>
+      <c r="AG123" s="2" t="inlineStr"/>
+      <c r="AH123" s="2" t="inlineStr"/>
+      <c r="AI123" s="2" t="inlineStr"/>
+      <c r="AJ123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>d71aa9b3f19748df</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>72081</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>0.602486</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>0.002485999999999877</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:53.673514Z</t>
+        </is>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr"/>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr"/>
+      <c r="Z124" s="2" t="inlineStr"/>
+      <c r="AA124" s="2" t="inlineStr"/>
+      <c r="AB124" s="2" t="inlineStr"/>
+      <c r="AC124" s="2" t="inlineStr"/>
+      <c r="AD124" s="2" t="inlineStr"/>
+      <c r="AE124" s="2" t="inlineStr"/>
+      <c r="AF124" s="2" t="inlineStr"/>
+      <c r="AG124" s="2" t="inlineStr"/>
+      <c r="AH124" s="2" t="inlineStr"/>
+      <c r="AI124" s="2" t="inlineStr"/>
+      <c r="AJ124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>fda3f21001a145a9</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>74328</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>0.535813</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr"/>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr"/>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>-0.013736549549549504</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:54.153981Z</t>
+        </is>
+      </c>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr"/>
+      <c r="W125" s="2" t="inlineStr"/>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr"/>
+      <c r="Z125" s="2" t="inlineStr"/>
+      <c r="AA125" s="2" t="inlineStr"/>
+      <c r="AB125" s="2" t="inlineStr"/>
+      <c r="AC125" s="2" t="inlineStr"/>
+      <c r="AD125" s="2" t="inlineStr"/>
+      <c r="AE125" s="2" t="inlineStr"/>
+      <c r="AF125" s="2" t="inlineStr"/>
+      <c r="AG125" s="2" t="inlineStr"/>
+      <c r="AH125" s="2" t="inlineStr"/>
+      <c r="AI125" s="2" t="inlineStr"/>
+      <c r="AJ125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>844a37bc36574d92</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>72729</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>0.645469</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr"/>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>0.26524086311787065</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:54.650443Z</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="inlineStr"/>
+      <c r="W126" s="2" t="inlineStr"/>
+      <c r="X126" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y126" s="2" t="inlineStr"/>
+      <c r="Z126" s="2" t="inlineStr"/>
+      <c r="AA126" s="2" t="inlineStr"/>
+      <c r="AB126" s="2" t="inlineStr"/>
+      <c r="AC126" s="2" t="inlineStr"/>
+      <c r="AD126" s="2" t="inlineStr"/>
+      <c r="AE126" s="2" t="inlineStr"/>
+      <c r="AF126" s="2" t="inlineStr"/>
+      <c r="AG126" s="2" t="inlineStr"/>
+      <c r="AH126" s="2" t="inlineStr"/>
+      <c r="AI126" s="2" t="inlineStr"/>
+      <c r="AJ126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>945d4be0553c49bf</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>74329</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>0.681484</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr"/>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>0.30125586311787067</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:55.156966Z</t>
+        </is>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr"/>
+      <c r="W127" s="2" t="inlineStr"/>
+      <c r="X127" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y127" s="2" t="inlineStr"/>
+      <c r="Z127" s="2" t="inlineStr"/>
+      <c r="AA127" s="2" t="inlineStr"/>
+      <c r="AB127" s="2" t="inlineStr"/>
+      <c r="AC127" s="2" t="inlineStr"/>
+      <c r="AD127" s="2" t="inlineStr"/>
+      <c r="AE127" s="2" t="inlineStr"/>
+      <c r="AF127" s="2" t="inlineStr"/>
+      <c r="AG127" s="2" t="inlineStr"/>
+      <c r="AH127" s="2" t="inlineStr"/>
+      <c r="AI127" s="2" t="inlineStr"/>
+      <c r="AJ127" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ97"/>
+  <autoFilter ref="A1:AJ127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ127"/>
+  <dimension ref="A1:AJ129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12972,14 +12972,34 @@
       <c r="W119" s="2" t="inlineStr"/>
       <c r="X119" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y119" s="2" t="inlineStr"/>
-      <c r="Z119" s="2" t="inlineStr"/>
-      <c r="AA119" s="2" t="inlineStr"/>
-      <c r="AB119" s="2" t="inlineStr"/>
-      <c r="AC119" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z119" s="2" t="inlineStr">
+        <is>
+          <t>0.680000</t>
+        </is>
+      </c>
+      <c r="AA119" s="2" t="inlineStr">
+        <is>
+          <t>-0.000511</t>
+        </is>
+      </c>
+      <c r="AB119" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:26:23.844338Z</t>
+        </is>
+      </c>
       <c r="AD119" s="2" t="inlineStr"/>
       <c r="AE119" s="2" t="inlineStr"/>
       <c r="AF119" s="2" t="inlineStr"/>
@@ -13804,8 +13824,212 @@
       <c r="AI127" s="2" t="inlineStr"/>
       <c r="AJ127" s="2" t="inlineStr"/>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>58606777afea4859</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>7611cb925b0bdd8cda78eee9a465c4db63ed56bf3e0e41982af2c70978a81fdb</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>72729</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>0.665399</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>0.1959154319248826</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:07.387751Z</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr"/>
+      <c r="W128" s="2" t="inlineStr"/>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y128" s="2" t="inlineStr"/>
+      <c r="Z128" s="2" t="inlineStr"/>
+      <c r="AA128" s="2" t="inlineStr"/>
+      <c r="AB128" s="2" t="inlineStr"/>
+      <c r="AC128" s="2" t="inlineStr"/>
+      <c r="AD128" s="2" t="inlineStr"/>
+      <c r="AE128" s="2" t="inlineStr"/>
+      <c r="AF128" s="2" t="inlineStr"/>
+      <c r="AG128" s="2" t="inlineStr"/>
+      <c r="AH128" s="2" t="inlineStr"/>
+      <c r="AI128" s="2" t="inlineStr"/>
+      <c r="AJ128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>acf5107432314754</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>7611cb925b0bdd8cda78eee9a465c4db63ed56bf3e0e41982af2c70978a81fdb</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>74329</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>0.681177</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr"/>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr"/>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>0.27134093442622953</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:07.918561Z</t>
+        </is>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr"/>
+      <c r="W129" s="2" t="inlineStr"/>
+      <c r="X129" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y129" s="2" t="inlineStr"/>
+      <c r="Z129" s="2" t="inlineStr"/>
+      <c r="AA129" s="2" t="inlineStr"/>
+      <c r="AB129" s="2" t="inlineStr"/>
+      <c r="AC129" s="2" t="inlineStr"/>
+      <c r="AD129" s="2" t="inlineStr"/>
+      <c r="AE129" s="2" t="inlineStr"/>
+      <c r="AF129" s="2" t="inlineStr"/>
+      <c r="AG129" s="2" t="inlineStr"/>
+      <c r="AH129" s="2" t="inlineStr"/>
+      <c r="AI129" s="2" t="inlineStr"/>
+      <c r="AJ129" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ127"/>
+  <autoFilter ref="A1:AJ129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>